--- a/public/exports/Номенклатура Weissgauff в загрузку 1С.xlsx
+++ b/public/exports/Номенклатура Weissgauff в загрузку 1С.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>4393720602590</t>
+          <t>4393720602590; 4393720602651</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>4393720600978</t>
+          <t>4393720600978; 2020004344977</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>4393720600909</t>
+          <t>4393720600909; 2020004341426</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>4393720602811</t>
+          <t>4393720602811; 2020004366238</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>4393720472537</t>
+          <t>4393720472537; 2020004308993</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>4393720472469</t>
+          <t>4393720472469; 2020004309457</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>4393720600541</t>
+          <t>4393720600541; 2020004335784</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>4393720472520</t>
+          <t>4393720472520; 2020004309518</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="B455" s="3" t="inlineStr">
         <is>
-          <t>4393720600572</t>
+          <t>4393720600572; 2020004335821</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>4393720600190</t>
+          <t>4393720600190; 2020004332189</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -18612,7 +18612,7 @@
       </c>
       <c r="B483" s="3" t="inlineStr">
         <is>
-          <t>4393720450566</t>
+          <t>4393720450566; 2020004210081</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>4393720477679</t>
+          <t>4393720477679; 2020004330840</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="B514" s="3" t="inlineStr">
         <is>
-          <t>4393720473749</t>
+          <t>4393720473749; 2020004314932</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="B532" s="3" t="inlineStr">
         <is>
-          <t>4393720445432</t>
+          <t>4393720445432; 2020004118417</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="B544" s="3" t="inlineStr">
         <is>
-          <t>4393720467885</t>
+          <t>4393720467885; 2020003813511</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="B545" s="3" t="inlineStr">
         <is>
-          <t>4393720477709</t>
+          <t>4393720477709; 2020004330871</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="B546" s="3" t="inlineStr">
         <is>
-          <t>4393720600657</t>
+          <t>4393720600657; 2020004336446</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="B563" s="3" t="inlineStr">
         <is>
-          <t>4393720445456</t>
+          <t>4393720445456; 2020004118431</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="B573" s="3" t="inlineStr">
         <is>
-          <t>4393720602743</t>
+          <t>4393720602743; 2020004361882</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="B581" s="3" t="inlineStr">
         <is>
-          <t>4393720467960</t>
+          <t>4393720467960; 2020003245992</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="B619" s="3" t="inlineStr">
         <is>
-          <t>4393720439806</t>
+          <t>4393720439806; 2020003245909</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="B630" s="3" t="inlineStr">
         <is>
-          <t>4393720470885</t>
+          <t>4393720470885; 2020003335341</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="B660" s="3" t="inlineStr">
         <is>
-          <t>4393720601425</t>
+          <t>4393720601425; 2020004340689</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="B703" s="3" t="inlineStr">
         <is>
-          <t>4602807496152</t>
+          <t>4602807496152; 2020004309549</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="B704" s="3" t="inlineStr">
         <is>
-          <t>4393720450696</t>
+          <t>4393720450696; 2020004231581</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="B728" s="3" t="inlineStr">
         <is>
-          <t>4393720602934</t>
+          <t>4393720602934; 2020004367235</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -28666,7 +28666,7 @@
       </c>
       <c r="B748" s="3" t="inlineStr">
         <is>
-          <t>4393720465416</t>
+          <t>4393720465416; 2020003813474</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="B774" s="3" t="inlineStr">
         <is>
-          <t>4393720606253</t>
+          <t>4393720606253; 4393720606772</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="B878" s="3" t="inlineStr">
         <is>
-          <t>4393720603559</t>
+          <t>4393720603559; 2020004374271</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -34556,7 +34556,7 @@
       </c>
       <c r="B904" s="3" t="inlineStr">
         <is>
-          <t>4393720602736</t>
+          <t>4393720602736; 2020004363145</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -34898,7 +34898,7 @@
       </c>
       <c r="B913" s="3" t="inlineStr">
         <is>
-          <t>4393720602460</t>
+          <t>4393720602460; 2020004351302</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -34936,7 +34936,7 @@
       </c>
       <c r="B914" s="3" t="inlineStr">
         <is>
-          <t>4393720472292</t>
+          <t>4393720472292; 2020004308719</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -35012,7 +35012,7 @@
       </c>
       <c r="B916" s="3" t="inlineStr">
         <is>
-          <t>4393720605058</t>
+          <t>4393720605058; 2020004384836</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="B924" s="3" t="inlineStr">
         <is>
-          <t>4393720610854</t>
+          <t>4393720610854; 4640563530079</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -35992,7 +35992,7 @@
       </c>
       <c r="B942" s="3" t="inlineStr">
         <is>
-          <t>4393720600947</t>
+          <t>4393720600947; 2020004342560</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="B1004" s="3" t="inlineStr">
         <is>
-          <t>4393720601586</t>
+          <t>4393720601586; 2020004352347</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="B1042" s="3" t="inlineStr">
         <is>
-          <t>4393720458937</t>
+          <t>4393720458937; 2020004260628</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="B1049" s="3" t="inlineStr">
         <is>
-          <t>4393720477891</t>
+          <t>4393720477891; 2020004329790</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -42240,7 +42240,7 @@
       </c>
       <c r="B1108" s="3" t="inlineStr">
         <is>
-          <t>4393720476047</t>
+          <t>4393720476047; 2020004321947</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
@@ -42842,7 +42842,7 @@
       </c>
       <c r="B1124" s="3" t="inlineStr">
         <is>
-          <t>4393720600763</t>
+          <t>4393720600763; 2020004337924</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="B1127" s="3" t="inlineStr">
         <is>
-          <t>4393720475910</t>
+          <t>4393720475910; 2020004321756</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="B1131" s="3" t="inlineStr">
         <is>
-          <t>4393720447931</t>
+          <t>4393720447931; 2020004194404</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="B1162" s="3" t="inlineStr">
         <is>
-          <t>4393720447900</t>
+          <t>4393720447900; 2020004194275</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="B1165" s="3" t="inlineStr">
         <is>
-          <t>4393720458975</t>
+          <t>4393720458975; 2020004260666</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
@@ -49888,7 +49888,7 @@
       </c>
       <c r="B1310" s="3" t="inlineStr">
         <is>
-          <t>4393720477037</t>
+          <t>4393720477037; 2020004328328</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr">
@@ -50648,7 +50648,7 @@
       </c>
       <c r="B1330" s="3" t="inlineStr">
         <is>
-          <t>4393720605393</t>
+          <t>4393720605393; 2020004383297</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr">
@@ -52040,7 +52040,7 @@
       </c>
       <c r="B1367" s="3" t="inlineStr">
         <is>
-          <t>4393720473282</t>
+          <t>4393720473282; 2020004313690</t>
         </is>
       </c>
       <c r="C1367" t="inlineStr">
@@ -52610,7 +52610,7 @@
       </c>
       <c r="B1382" s="3" t="inlineStr">
         <is>
-          <t>4393720476603</t>
+          <t>4393720476603; 2020004325846</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr">
@@ -53776,7 +53776,7 @@
       </c>
       <c r="B1413" s="3" t="inlineStr">
         <is>
-          <t>4393720472933</t>
+          <t>4393720472933; 2020004309723</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
@@ -57352,7 +57352,7 @@
       </c>
       <c r="B1508" s="3" t="inlineStr">
         <is>
-          <t>4393720472919</t>
+          <t>4393720472919; 2020004309709</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr">
@@ -58298,7 +58298,7 @@
       </c>
       <c r="B1533" s="3" t="inlineStr">
         <is>
-          <t>4393720471059</t>
+          <t>4393720471059; 2020004306487</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
@@ -61246,7 +61246,7 @@
       </c>
       <c r="B1611" s="3" t="inlineStr">
         <is>
-          <t>4393720601142</t>
+          <t>4393720601142; 2020004360724</t>
         </is>
       </c>
       <c r="C1611" t="inlineStr">
@@ -62346,7 +62346,7 @@
       </c>
       <c r="B1640" s="3" t="inlineStr">
         <is>
-          <t>4393720472155</t>
+          <t>4393720472155; 2020004308016</t>
         </is>
       </c>
       <c r="C1640" t="inlineStr">
@@ -69400,7 +69400,7 @@
       </c>
       <c r="B1827" s="3" t="inlineStr">
         <is>
-          <t>4393720609537</t>
+          <t>4393720609537; 4640213440079</t>
         </is>
       </c>
       <c r="C1827" t="inlineStr">
@@ -70554,7 +70554,7 @@
       </c>
       <c r="B1858" s="3" t="inlineStr">
         <is>
-          <t>4393720477297</t>
+          <t>4393720477297; 2020004330246</t>
         </is>
       </c>
       <c r="C1858" t="inlineStr">
@@ -73338,7 +73338,7 @@
       </c>
       <c r="B1932" s="3" t="inlineStr">
         <is>
-          <t>4393720473985</t>
+          <t>4393720473985; 2020004315250</t>
         </is>
       </c>
       <c r="C1932" t="inlineStr">
@@ -74098,7 +74098,7 @@
       </c>
       <c r="B1952" s="3" t="inlineStr">
         <is>
-          <t>4393720600855</t>
+          <t>4393720600855; 2020004341181</t>
         </is>
       </c>
       <c r="C1952" t="inlineStr">
@@ -74136,7 +74136,7 @@
       </c>
       <c r="B1953" s="3" t="inlineStr">
         <is>
-          <t>4393720600862</t>
+          <t>4393720600862; 2020004341235</t>
         </is>
       </c>
       <c r="C1953" t="inlineStr">
